--- a/AAII_Financials/Quarterly/CDNS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CDNS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>CDNS</t>
   </si>
@@ -672,525 +672,538 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="15.85546875" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="15.85546875" style="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="18.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.5703125" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="15.85546875" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" style="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="18.140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="15.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.5703125" style="1" customWidth="1"/>
+    <col min="23" max="16384" width="15.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="5">
+      <c r="O7" s="5">
         <v>45199</v>
       </c>
-      <c r="O7" s="5">
+      <c r="P7" s="5">
         <v>45107</v>
       </c>
-      <c r="P7" s="5">
+      <c r="Q7" s="5">
         <v>45016</v>
       </c>
-      <c r="Q7" s="5">
+      <c r="R7" s="5">
         <v>44926</v>
       </c>
-      <c r="R7" s="5">
+      <c r="S7" s="5">
         <v>44835</v>
       </c>
-      <c r="S7" s="5">
+      <c r="T7" s="5">
         <v>44744</v>
       </c>
-      <c r="T7" s="5">
+      <c r="U7" s="5">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44563</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44198</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44100</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44009</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43918</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43827</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43463</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43099</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1584500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1474200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1440100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1338800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1275400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1242400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1356000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1215500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1060700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1009100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1068600</v>
       </c>
-      <c r="N8" s="6">
+      <c r="O8" s="6">
         <v>1023100</v>
       </c>
-      <c r="O8" s="6">
+      <c r="P8" s="6">
         <v>976600</v>
       </c>
-      <c r="P8" s="6">
+      <c r="Q8" s="6">
         <v>1021700</v>
       </c>
-      <c r="Q8" s="6">
+      <c r="R8" s="6">
         <v>899900</v>
       </c>
-      <c r="R8" s="6">
+      <c r="S8" s="6">
         <v>902600</v>
       </c>
-      <c r="S8" s="6">
+      <c r="T8" s="6">
         <v>857500</v>
       </c>
-      <c r="T8" s="6">
+      <c r="U8" s="6">
         <v>901800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>773000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>750900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>728300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>736000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>759900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>666600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>638400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>618000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>599600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>579600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>580400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>576700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>569900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>532500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>518400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>517300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>501700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>485400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>479000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>476900</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>469000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>446200</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>239300</v>
+      </c>
+      <c r="E9" s="3">
         <v>214500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>188800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>182200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>184200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>167100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>220000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>163000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>139300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>125200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>104100</v>
       </c>
-      <c r="N9" s="6">
+      <c r="O9" s="6">
         <v>109600</v>
       </c>
-      <c r="O9" s="6">
+      <c r="P9" s="6">
         <v>96900</v>
       </c>
-      <c r="P9" s="6">
+      <c r="Q9" s="6">
         <v>124500</v>
       </c>
-      <c r="Q9" s="6">
+      <c r="R9" s="6">
         <v>93500</v>
       </c>
-      <c r="R9" s="6">
+      <c r="S9" s="6">
         <v>87600</v>
       </c>
-      <c r="S9" s="6">
+      <c r="T9" s="6">
         <v>92700</v>
       </c>
-      <c r="T9" s="6">
+      <c r="U9" s="6">
         <v>97800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>69700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>76600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>76800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>84000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>73500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>82300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>75200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>74500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>73300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>61000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>61500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>70600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>76100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>60500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>59000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>63200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>60300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>54500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>60800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>61800</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>76000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>56600</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1345100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1259700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1251400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1156600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1091300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1075200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1136000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1052500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>921400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>883900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>964500</v>
       </c>
-      <c r="N10" s="6">
+      <c r="O10" s="6">
         <v>913500</v>
       </c>
-      <c r="O10" s="6">
+      <c r="P10" s="6">
         <v>879700</v>
       </c>
-      <c r="P10" s="6">
+      <c r="Q10" s="6">
         <v>897200</v>
       </c>
-      <c r="Q10" s="6">
+      <c r="R10" s="6">
         <v>806400</v>
       </c>
-      <c r="R10" s="6">
+      <c r="S10" s="6">
         <v>815000</v>
       </c>
-      <c r="S10" s="6">
+      <c r="T10" s="6">
         <v>764800</v>
       </c>
-      <c r="T10" s="6">
+      <c r="U10" s="6">
         <v>804000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>703300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>674300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>651500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>652000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>686400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>584300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>563200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>543500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>526300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>518600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>518900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>506100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>493800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>472000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>459400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>454100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>441400</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>430900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>418200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>415100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>393000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>389600</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1204,14 +1217,14 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="6"/>
+      <c r="N11" s="3"/>
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
       <c r="S11" s="6"/>
       <c r="T11" s="6"/>
-      <c r="U11" s="3"/>
+      <c r="U11" s="6"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
@@ -1233,130 +1246,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>531300</v>
+      </c>
+      <c r="E12" s="3">
         <v>508400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>464600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>423000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>442100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>439100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>392000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>407400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>370700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>379000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>367400</v>
       </c>
-      <c r="N12" s="6">
+      <c r="O12" s="6">
         <v>369600</v>
       </c>
-      <c r="O12" s="6">
+      <c r="P12" s="6">
         <v>354400</v>
       </c>
-      <c r="P12" s="6">
+      <c r="Q12" s="6">
         <v>350300</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="R12" s="6">
         <v>350400</v>
       </c>
-      <c r="R12" s="6">
+      <c r="S12" s="6">
         <v>323600</v>
       </c>
-      <c r="S12" s="6">
+      <c r="T12" s="6">
         <v>286600</v>
       </c>
-      <c r="T12" s="6">
+      <c r="U12" s="6">
         <v>290900</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>289000</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>289100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>285200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>271000</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>290300</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>250900</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>250800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>241700</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>235400</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>240500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>231800</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>228200</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>218300</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>223200</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>219100</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>224200</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>203500</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>206600</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>195900</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>198300</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>181500</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>191500</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1390,7 +1407,7 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="6">
+      <c r="N13" s="3">
         <v>0</v>
       </c>
       <c r="O13" s="6">
@@ -1411,7 +1428,7 @@
       <c r="T13" s="6">
         <v>0</v>
       </c>
-      <c r="U13" s="3">
+      <c r="U13" s="6">
         <v>0</v>
       </c>
       <c r="V13" s="3">
@@ -1477,50 +1494,53 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-80900</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-39700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>53200</v>
       </c>
-      <c r="G14" s="3">
-        <v>94100</v>
-      </c>
       <c r="H14" s="3">
+        <v>86400</v>
+      </c>
+      <c r="I14" s="3">
         <v>5300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>23200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>37100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-21800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-59700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-26900</v>
       </c>
-      <c r="N14" s="6">
+      <c r="O14" s="6">
         <v>4300</v>
       </c>
-      <c r="O14" s="6">
+      <c r="P14" s="6">
         <v>600</v>
       </c>
-      <c r="P14" s="6">
-        <v>0</v>
-      </c>
       <c r="Q14" s="6">
         <v>0</v>
       </c>
@@ -1533,129 +1553,132 @@
       <c r="T14" s="6">
         <v>0</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="6">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>10500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>9800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>-300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>-700</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>-200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>-2000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>12200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-100</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>-900</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>-1800</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>26300</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E15" s="3">
         <v>20200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>5400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>5000</v>
       </c>
-      <c r="N15" s="6">
+      <c r="O15" s="6">
         <v>4600</v>
-      </c>
-      <c r="O15" s="6">
-        <v>4300</v>
       </c>
       <c r="P15" s="6">
         <v>4300</v>
       </c>
       <c r="Q15" s="6">
+        <v>4300</v>
+      </c>
+      <c r="R15" s="6">
         <v>4900</v>
       </c>
-      <c r="R15" s="6">
+      <c r="S15" s="6">
         <v>3900</v>
       </c>
-      <c r="S15" s="6">
+      <c r="T15" s="6">
         <v>4600</v>
       </c>
-      <c r="T15" s="6">
-        <v>5000</v>
-      </c>
-      <c r="U15" s="3">
+      <c r="U15" s="6">
         <v>5000</v>
       </c>
       <c r="V15" s="3">
@@ -1665,34 +1688,34 @@
         <v>5000</v>
       </c>
       <c r="X15" s="3">
+        <v>5000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>4600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>4200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>2900</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>3200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>3300</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>3500</v>
       </c>
       <c r="AH15" s="3">
         <v>3500</v>
@@ -1701,19 +1724,19 @@
         <v>3500</v>
       </c>
       <c r="AJ15" s="3">
-        <v>3600</v>
+        <v>3500</v>
       </c>
       <c r="AK15" s="3">
         <v>3600</v>
       </c>
       <c r="AL15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AM15" s="3">
         <v>3500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>3800</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>3900</v>
       </c>
       <c r="AO15" s="3">
         <v>3900</v>
@@ -1721,8 +1744,11 @@
       <c r="AP15" s="3">
         <v>3900</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>3900</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1733,14 +1759,14 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="3"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
-      <c r="U16" s="3"/>
+      <c r="U16" s="6"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
@@ -1762,252 +1788,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>1131700</v>
+      </c>
+      <c r="E17" s="3">
         <v>1036400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>967400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>869100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>901100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>879000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>890500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>839900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>763400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>758900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>730900</v>
       </c>
-      <c r="N17" s="6">
+      <c r="O17" s="6">
         <v>714300</v>
       </c>
-      <c r="O17" s="6">
+      <c r="P17" s="6">
         <v>674200</v>
       </c>
-      <c r="P17" s="6">
+      <c r="Q17" s="6">
         <v>699200</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="R17" s="6">
         <v>688800</v>
       </c>
-      <c r="R17" s="6">
+      <c r="S17" s="6">
         <v>641800</v>
       </c>
-      <c r="S17" s="6">
+      <c r="T17" s="6">
         <v>574600</v>
       </c>
-      <c r="T17" s="6">
+      <c r="U17" s="6">
         <v>582800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>577400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>556900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>542800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>532100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>574900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>497300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>486500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>478600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>490700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>458800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>446700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>448300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>456200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>428800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>425300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>431500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>420400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>405000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>396300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>397300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>415900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>379400</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>452800</v>
+      </c>
+      <c r="E18" s="3">
         <v>437800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>472700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>469800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>374400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>363400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>465500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>375600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>297200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>250200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>337800</v>
       </c>
-      <c r="N18" s="6">
+      <c r="O18" s="6">
         <v>308800</v>
       </c>
-      <c r="O18" s="6">
+      <c r="P18" s="6">
         <v>302400</v>
       </c>
-      <c r="P18" s="6">
+      <c r="Q18" s="6">
         <v>322500</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="R18" s="6">
         <v>211100</v>
       </c>
-      <c r="R18" s="6">
+      <c r="S18" s="6">
         <v>260800</v>
       </c>
-      <c r="S18" s="6">
+      <c r="T18" s="6">
         <v>282900</v>
       </c>
-      <c r="T18" s="6">
+      <c r="U18" s="6">
         <v>319000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>195600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>194000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>185500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>203900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>185000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>169300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>151900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>139400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>108900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>120800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>133700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>128400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>113700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>103700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>93100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>85800</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>81300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>80400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>82700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>79600</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>53100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>66800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2021,14 +2054,14 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-      <c r="N19" s="6"/>
+      <c r="N19" s="3"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
       <c r="Q19" s="6"/>
       <c r="R19" s="6"/>
       <c r="S19" s="6"/>
       <c r="T19" s="6"/>
-      <c r="U19" s="3"/>
+      <c r="U19" s="6"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
@@ -2050,618 +2083,634 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E20" s="3">
         <v>1000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>14700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>19400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-3300</v>
-      </c>
       <c r="H20" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1000</v>
       </c>
-      <c r="N20" s="6">
+      <c r="O20" s="6">
         <v>3900</v>
       </c>
-      <c r="O20" s="6">
+      <c r="P20" s="6">
         <v>2000</v>
       </c>
-      <c r="P20" s="6">
+      <c r="Q20" s="6">
         <v>8300</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="R20" s="6">
         <v>8500</v>
       </c>
-      <c r="R20" s="6">
+      <c r="S20" s="6">
         <v>-3100</v>
       </c>
-      <c r="S20" s="6">
+      <c r="T20" s="6">
         <v>-5900</v>
       </c>
-      <c r="T20" s="6">
+      <c r="U20" s="6">
         <v>-4900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>6100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>1800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>1100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>12400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>1100</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>5500</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>488900</v>
+      </c>
+      <c r="E21" s="3">
         <v>457100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>469600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>460600</v>
       </c>
-      <c r="G21" s="3">
-        <v>386900</v>
-      </c>
       <c r="H21" s="3">
+        <v>379200</v>
+      </c>
+      <c r="I21" s="3">
         <v>372800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>471700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>387200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>304600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>254900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>341700</v>
       </c>
-      <c r="N21" s="6">
+      <c r="O21" s="6">
         <v>309500</v>
       </c>
-      <c r="O21" s="6">
+      <c r="P21" s="6">
         <v>304800</v>
       </c>
-      <c r="P21" s="6">
+      <c r="Q21" s="6">
         <v>365100</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="R21" s="6">
         <v>253500</v>
       </c>
-      <c r="R21" s="6">
+      <c r="S21" s="6">
         <v>288200</v>
       </c>
-      <c r="S21" s="6">
+      <c r="T21" s="6">
         <v>309800</v>
       </c>
-      <c r="T21" s="6">
+      <c r="U21" s="6">
         <v>348900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>233700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>228100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>223200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>242900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>229700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>208200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>193200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>168100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>141000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>151200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>165000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>163400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>142700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>134500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>126600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>114500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>112600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>121100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>113000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>109600</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>88500</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>96600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E22" s="3">
         <v>31600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>29400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>28900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9000</v>
       </c>
-      <c r="N22" s="6">
+      <c r="O22" s="6">
         <v>9100</v>
       </c>
-      <c r="O22" s="6">
+      <c r="P22" s="6">
         <v>8900</v>
       </c>
-      <c r="P22" s="6">
+      <c r="Q22" s="6">
         <v>9300</v>
       </c>
-      <c r="Q22" s="6">
+      <c r="R22" s="6">
         <v>9100</v>
       </c>
-      <c r="R22" s="6">
+      <c r="S22" s="6">
         <v>5500</v>
       </c>
-      <c r="S22" s="6">
+      <c r="T22" s="6">
         <v>4300</v>
       </c>
-      <c r="T22" s="6">
+      <c r="U22" s="6">
         <v>4100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4600</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>4200</v>
       </c>
       <c r="AD22" s="3">
         <v>4200</v>
       </c>
       <c r="AE22" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>5000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>4300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>6700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7000</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>6700</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>6200</v>
       </c>
       <c r="AM22" s="3">
         <v>6200</v>
       </c>
       <c r="AN22" s="3">
+        <v>6200</v>
+      </c>
+      <c r="AO22" s="3">
         <v>6500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>6400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>6100</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>510200</v>
+      </c>
+      <c r="E23" s="3">
         <v>428100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>493000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>392800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>280600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>355700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>436700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>333400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>315700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>310000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>362100</v>
       </c>
-      <c r="N23" s="6">
+      <c r="O23" s="6">
         <v>300000</v>
       </c>
-      <c r="O23" s="6">
+      <c r="P23" s="6">
         <v>298400</v>
       </c>
-      <c r="P23" s="6">
+      <c r="Q23" s="6">
         <v>321500</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="R23" s="6">
         <v>210500</v>
       </c>
-      <c r="R23" s="6">
+      <c r="S23" s="6">
         <v>252300</v>
       </c>
-      <c r="S23" s="6">
+      <c r="T23" s="6">
         <v>272600</v>
       </c>
-      <c r="T23" s="6">
+      <c r="U23" s="6">
         <v>309900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>194100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>188700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>183300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>202400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>186200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>165700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>150700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>130200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>105400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>116700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>128600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>128200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>108600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>99600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>90000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>78200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>77000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>86500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>77400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>74200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>52200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>63600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E24" s="3">
         <v>92400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>104800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>105700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>120600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>82100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>96400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>95300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>86200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>62400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38200</v>
       </c>
-      <c r="N24" s="6">
+      <c r="O24" s="6">
         <v>45600</v>
       </c>
-      <c r="O24" s="6">
+      <c r="P24" s="6">
         <v>77300</v>
       </c>
-      <c r="P24" s="6">
+      <c r="Q24" s="6">
         <v>79700</v>
       </c>
-      <c r="Q24" s="6">
+      <c r="R24" s="6">
         <v>-29900</v>
       </c>
-      <c r="R24" s="6">
+      <c r="S24" s="6">
         <v>66000</v>
       </c>
-      <c r="S24" s="6">
+      <c r="T24" s="6">
         <v>85700</v>
       </c>
-      <c r="T24" s="6">
+      <c r="U24" s="6">
         <v>74600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>12400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>27400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>15300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>12500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>19400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-553300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>21400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>14200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>14900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>188100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>5400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>8200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>5900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>13800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-1100</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2695,7 +2744,7 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="6">
+      <c r="N25" s="3">
         <v>0</v>
       </c>
       <c r="O25" s="6">
@@ -2716,7 +2765,7 @@
       <c r="T25" s="6">
         <v>0</v>
       </c>
-      <c r="U25" s="3">
+      <c r="U25" s="6">
         <v>0</v>
       </c>
       <c r="V25" s="3">
@@ -2782,252 +2831,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E26" s="3">
         <v>335700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>388100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>287100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>160100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>273600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>340200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>238100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>229500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>247600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>323900</v>
       </c>
-      <c r="N26" s="6">
+      <c r="O26" s="6">
         <v>254300</v>
       </c>
-      <c r="O26" s="6">
+      <c r="P26" s="6">
         <v>221100</v>
       </c>
-      <c r="P26" s="6">
+      <c r="Q26" s="6">
         <v>241800</v>
       </c>
-      <c r="Q26" s="6">
+      <c r="R26" s="6">
         <v>240400</v>
       </c>
-      <c r="R26" s="6">
+      <c r="S26" s="6">
         <v>186300</v>
       </c>
-      <c r="S26" s="6">
+      <c r="T26" s="6">
         <v>186900</v>
       </c>
-      <c r="T26" s="6">
+      <c r="U26" s="6">
         <v>235300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>176600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>176300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>155900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>187200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>173700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>161600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>131300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>124000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>658700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>101500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>107200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>94400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>99300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>75500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-111100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>81200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>69100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>68300</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>38500</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E27" s="3">
         <v>335700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>388100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>287100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>160100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>273600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>340200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>238100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>229500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>247600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>323900</v>
       </c>
-      <c r="N27" s="6">
+      <c r="O27" s="6">
         <v>254300</v>
       </c>
-      <c r="O27" s="6">
+      <c r="P27" s="6">
         <v>221100</v>
       </c>
-      <c r="P27" s="6">
+      <c r="Q27" s="6">
         <v>241800</v>
       </c>
-      <c r="Q27" s="6">
+      <c r="R27" s="6">
         <v>240400</v>
       </c>
-      <c r="R27" s="6">
+      <c r="S27" s="6">
         <v>186300</v>
       </c>
-      <c r="S27" s="6">
+      <c r="T27" s="6">
         <v>186900</v>
       </c>
-      <c r="T27" s="6">
+      <c r="U27" s="6">
         <v>235300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>176600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>176300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>155900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>187200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>173700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>161600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>131300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>124000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>658700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>101500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>107200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>121600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>94400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>99300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>75500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-111100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>81200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>69100</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>68300</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>38500</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3061,7 +3119,7 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="6">
+      <c r="N28" s="3">
         <v>0</v>
       </c>
       <c r="O28" s="6">
@@ -3082,7 +3140,7 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="3">
+      <c r="U28" s="6">
         <v>0</v>
       </c>
       <c r="V28" s="3">
@@ -3148,8 +3206,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3183,7 +3244,7 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="6">
+      <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="6">
@@ -3204,8 +3265,8 @@
       <c r="T29" s="6">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>24</v>
+      <c r="U29" s="6">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>24</v>
@@ -3228,35 +3289,35 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>4000</v>
       </c>
-      <c r="AH29" s="3">
-        <v>0</v>
-      </c>
       <c r="AI29" s="3">
         <v>0</v>
       </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>96700</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3270,8 +3331,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3305,7 +3369,7 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="6">
+      <c r="N30" s="3">
         <v>0</v>
       </c>
       <c r="O30" s="6">
@@ -3326,7 +3390,7 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="3">
+      <c r="U30" s="6">
         <v>0</v>
       </c>
       <c r="V30" s="3">
@@ -3392,8 +3456,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3427,7 +3494,7 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="6">
+      <c r="N31" s="3">
         <v>0</v>
       </c>
       <c r="O31" s="6">
@@ -3448,7 +3515,7 @@
       <c r="T31" s="6">
         <v>0</v>
       </c>
-      <c r="U31" s="3">
+      <c r="U31" s="6">
         <v>0</v>
       </c>
       <c r="V31" s="3">
@@ -3514,252 +3581,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-14700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-19400</v>
       </c>
-      <c r="G32" s="3">
-        <v>3300</v>
-      </c>
       <c r="H32" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1000</v>
       </c>
-      <c r="N32" s="6">
+      <c r="O32" s="6">
         <v>-3900</v>
       </c>
-      <c r="O32" s="6">
+      <c r="P32" s="6">
         <v>-2000</v>
       </c>
-      <c r="P32" s="6">
+      <c r="Q32" s="6">
         <v>-8300</v>
       </c>
-      <c r="Q32" s="6">
+      <c r="R32" s="6">
         <v>-8500</v>
       </c>
-      <c r="R32" s="6">
+      <c r="S32" s="6">
         <v>3100</v>
       </c>
-      <c r="S32" s="6">
+      <c r="T32" s="6">
         <v>5900</v>
       </c>
-      <c r="T32" s="6">
+      <c r="U32" s="6">
         <v>4900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-5500</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E33" s="3">
         <v>335700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>388100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>287100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>160100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>273600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>340200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>238100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>229500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>247600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>323900</v>
       </c>
-      <c r="N33" s="6">
+      <c r="O33" s="6">
         <v>254300</v>
       </c>
-      <c r="O33" s="6">
+      <c r="P33" s="6">
         <v>221100</v>
       </c>
-      <c r="P33" s="6">
+      <c r="Q33" s="6">
         <v>241800</v>
       </c>
-      <c r="Q33" s="6">
+      <c r="R33" s="6">
         <v>240400</v>
       </c>
-      <c r="R33" s="6">
+      <c r="S33" s="6">
         <v>186300</v>
       </c>
-      <c r="S33" s="6">
+      <c r="T33" s="6">
         <v>186900</v>
       </c>
-      <c r="T33" s="6">
+      <c r="U33" s="6">
         <v>235300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>176600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>176300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>155900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>187200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>173700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>161600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>131300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>124000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>659700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>101500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>107200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>120600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>98400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>99300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>72900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-14400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>81200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>69100</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>68300</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>38500</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3793,7 +3869,7 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="6">
+      <c r="N34" s="3">
         <v>0</v>
       </c>
       <c r="O34" s="6">
@@ -3814,7 +3890,7 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="3">
+      <c r="U34" s="6">
         <v>0</v>
       </c>
       <c r="V34" s="3">
@@ -3880,257 +3956,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E35" s="3">
         <v>335700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>388100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>287100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>160100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>273600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>340200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>238100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>229500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>247600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>323900</v>
       </c>
-      <c r="N35" s="6">
+      <c r="O35" s="6">
         <v>254300</v>
       </c>
-      <c r="O35" s="6">
+      <c r="P35" s="6">
         <v>221100</v>
       </c>
-      <c r="P35" s="6">
+      <c r="Q35" s="6">
         <v>241800</v>
       </c>
-      <c r="Q35" s="6">
+      <c r="R35" s="6">
         <v>240400</v>
       </c>
-      <c r="R35" s="6">
+      <c r="S35" s="6">
         <v>186300</v>
       </c>
-      <c r="S35" s="6">
+      <c r="T35" s="6">
         <v>186900</v>
       </c>
-      <c r="T35" s="6">
+      <c r="U35" s="6">
         <v>235300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>176600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>176300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>155900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>187200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>173700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>161600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>131300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>124000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>659700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>101500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>107200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>120600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>98400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>99300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>72900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-14400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>81200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>69100</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>68300</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>38500</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="5">
+      <c r="O38" s="5">
         <v>45199</v>
       </c>
-      <c r="O38" s="5">
+      <c r="P38" s="5">
         <v>45107</v>
       </c>
-      <c r="P38" s="5">
+      <c r="Q38" s="5">
         <v>45016</v>
       </c>
-      <c r="Q38" s="5">
+      <c r="R38" s="5">
         <v>44926</v>
       </c>
-      <c r="R38" s="5">
+      <c r="S38" s="5">
         <v>44835</v>
       </c>
-      <c r="S38" s="5">
+      <c r="T38" s="5">
         <v>44744</v>
       </c>
-      <c r="T38" s="5">
+      <c r="U38" s="5">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44563</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44198</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44100</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44009</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43918</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43827</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43463</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43099</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4144,14 +4229,14 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-      <c r="N39" s="6"/>
+      <c r="N39" s="3"/>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
       <c r="Q39" s="6"/>
       <c r="R39" s="6"/>
       <c r="S39" s="6"/>
       <c r="T39" s="6"/>
-      <c r="U39" s="3"/>
+      <c r="U39" s="6"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
@@ -4173,8 +4258,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4188,14 +4274,14 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-      <c r="N40" s="6"/>
+      <c r="N40" s="3"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
       <c r="S40" s="6"/>
       <c r="T40" s="6"/>
-      <c r="U40" s="3"/>
+      <c r="U40" s="6"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
@@ -4217,171 +4303,175 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1440400</v>
+      </c>
+      <c r="E41" s="3">
         <v>1406700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3001300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2753200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2822800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2777700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2644000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2786000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1059000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1012400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1008200</v>
       </c>
-      <c r="N41" s="6">
+      <c r="O41" s="6">
         <v>962000</v>
       </c>
-      <c r="O41" s="6">
+      <c r="P41" s="6">
         <v>873900</v>
       </c>
-      <c r="P41" s="6">
+      <c r="Q41" s="6">
         <v>917000</v>
       </c>
-      <c r="Q41" s="6">
+      <c r="R41" s="6">
         <v>882300</v>
       </c>
-      <c r="R41" s="6">
+      <c r="S41" s="6">
         <v>1026100</v>
       </c>
-      <c r="S41" s="6">
+      <c r="T41" s="6">
         <v>1029500</v>
       </c>
-      <c r="T41" s="6">
+      <c r="U41" s="6">
         <v>1134800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1088900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1013800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>847200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>743000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>928400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1306600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1189200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>946300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>705200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>655200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>633400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>538900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>533300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>544600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>819500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>747000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>688100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>678300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>656000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>544100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>465200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>524300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E42" s="3">
         <v>139500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>154200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>176800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>178200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>129700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>140600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>155300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>169700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>144600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>130400</v>
       </c>
-      <c r="N42" s="6">
-        <v>0</v>
-      </c>
       <c r="O42" s="6">
         <v>0</v>
       </c>
-      <c r="P42" s="6" t="s">
-        <v>24</v>
+      <c r="P42" s="6">
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="s">
         <v>24</v>
@@ -4395,8 +4485,8 @@
       <c r="T42" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -4431,282 +4521,291 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-      <c r="AG42" s="3" t="s">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>5400</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5500</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>4100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>3200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3500</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>3100</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1104800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1073400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>944900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>846400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>753800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>651700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>680500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>612300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>590300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>439800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>489200</v>
       </c>
-      <c r="N43" s="6">
+      <c r="O43" s="6">
         <v>440900</v>
       </c>
-      <c r="O43" s="6">
+      <c r="P43" s="6">
         <v>458500</v>
       </c>
-      <c r="P43" s="6">
+      <c r="Q43" s="6">
         <v>505400</v>
       </c>
-      <c r="Q43" s="6">
+      <c r="R43" s="6">
         <v>509500</v>
       </c>
-      <c r="R43" s="6">
+      <c r="S43" s="6">
         <v>429600</v>
       </c>
-      <c r="S43" s="6">
+      <c r="T43" s="6">
         <v>415000</v>
       </c>
-      <c r="T43" s="6">
+      <c r="U43" s="6">
         <v>380900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>344400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>335000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>396000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>395600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>348200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>309100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>323000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>300100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>314800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>283400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>248100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>277000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>307100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>256000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>227400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>231900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>190400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>170300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>153200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>180600</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>157200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>390400</v>
+      </c>
+      <c r="E44" s="3">
         <v>318000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>303500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>286200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>226200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>225600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>257700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>293400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>171500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>185800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>181700</v>
       </c>
-      <c r="N44" s="6">
+      <c r="O44" s="6">
         <v>163700</v>
       </c>
-      <c r="O44" s="6">
+      <c r="P44" s="6">
         <v>139600</v>
       </c>
-      <c r="P44" s="6">
+      <c r="Q44" s="6">
         <v>127600</v>
       </c>
-      <c r="Q44" s="6">
+      <c r="R44" s="6">
         <v>128000</v>
       </c>
-      <c r="R44" s="6">
+      <c r="S44" s="6">
         <v>114300</v>
       </c>
-      <c r="S44" s="6">
+      <c r="T44" s="6">
         <v>106400</v>
       </c>
-      <c r="T44" s="6">
+      <c r="U44" s="6">
         <v>110200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>115700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>101600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>90500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>76600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>76000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>48000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>43900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>60600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>55800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>66700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>49300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>37500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>28200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>30500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>28600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>30100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>33200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>36000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>31900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>30700</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>39500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>64500</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4740,258 +4839,264 @@
       <c r="M45" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="6" t="s">
+      <c r="N45" s="3" t="s">
         <v>24</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q45" s="6">
         <v>148600</v>
       </c>
-      <c r="Q45" s="6">
+      <c r="R45" s="6">
         <v>187000</v>
       </c>
-      <c r="R45" s="6">
+      <c r="S45" s="6">
         <v>100500</v>
       </c>
-      <c r="S45" s="6">
+      <c r="T45" s="6">
         <v>106700</v>
       </c>
-      <c r="T45" s="6">
+      <c r="U45" s="6">
         <v>109100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>166700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>92600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>123400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>134500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>126000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>72800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>83700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>92600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>93600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>44600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>48400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>64600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>82500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>51800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>47700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>55500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>63800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>42400</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>39200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>41100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>37100</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>43000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3221900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3180400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4669700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4287000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4222500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3998100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4016100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4099900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2196400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1929900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1976200</v>
       </c>
-      <c r="N46" s="6">
+      <c r="O46" s="6">
         <v>1824500</v>
       </c>
-      <c r="O46" s="6">
+      <c r="P46" s="6">
         <v>1643100</v>
       </c>
-      <c r="P46" s="6">
+      <c r="Q46" s="6">
         <v>1698500</v>
       </c>
-      <c r="Q46" s="6">
+      <c r="R46" s="6">
         <v>1706800</v>
       </c>
-      <c r="R46" s="6">
+      <c r="S46" s="6">
         <v>1670500</v>
       </c>
-      <c r="S46" s="6">
+      <c r="T46" s="6">
         <v>1657600</v>
       </c>
-      <c r="T46" s="6">
+      <c r="U46" s="6">
         <v>1734900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1715800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1543000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1457100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1349700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1478600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1736500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1639800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1399500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1169300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1049900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>979200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>917900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>951100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>888400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1129100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1069900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>980000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>931100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>883500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>800000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>702000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>792300</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>89600</v>
+      </c>
+      <c r="E47" s="3">
         <v>83600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>67500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>128900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>130800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>132500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>124100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>105800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>108100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>138300</v>
-      </c>
-      <c r="N47" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P47" s="6">
-        <v>0</v>
+      <c r="P47" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="Q47" s="6">
         <v>0</v>
@@ -5005,7 +5110,7 @@
       <c r="T47" s="6">
         <v>0</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="6">
         <v>0</v>
       </c>
       <c r="V47" s="3">
@@ -5026,297 +5131,306 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>138200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>143300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>148400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>153600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>4400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>9400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>12200</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>11600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>13300</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>13100</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>560200</v>
+      </c>
+      <c r="E48" s="3">
         <v>536900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>693000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>494700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>482100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>466300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>604400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>448700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>449400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>433000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>554000</v>
       </c>
-      <c r="N48" s="6">
+      <c r="O48" s="6">
         <v>379800</v>
       </c>
-      <c r="O48" s="6">
+      <c r="P48" s="6">
         <v>370200</v>
       </c>
-      <c r="P48" s="6">
+      <c r="Q48" s="6">
         <v>373000</v>
       </c>
-      <c r="Q48" s="6">
+      <c r="R48" s="6">
         <v>371500</v>
       </c>
-      <c r="R48" s="6">
+      <c r="S48" s="6">
         <v>348200</v>
       </c>
-      <c r="S48" s="6">
+      <c r="T48" s="6">
         <v>316700</v>
       </c>
-      <c r="T48" s="6">
+      <c r="U48" s="6">
         <v>310700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>305900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>303300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>302000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>305100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>311100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>288200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>282700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>281200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>376200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>364000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>366800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>347600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>252600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>248200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>252200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>249800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>251300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>244600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>249100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>243900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>238600</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>240600</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6789200</v>
+      </c>
+      <c r="E49" s="3">
         <v>6862800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3467400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3317400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3218800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3003900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2973400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3155800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3081800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1909800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1872700</v>
       </c>
-      <c r="N49" s="6">
+      <c r="O49" s="6">
         <v>1848100</v>
       </c>
-      <c r="O49" s="6">
+      <c r="P49" s="6">
         <v>1769500</v>
       </c>
-      <c r="P49" s="6">
+      <c r="Q49" s="6">
         <v>1719400</v>
       </c>
-      <c r="Q49" s="6">
+      <c r="R49" s="6">
         <v>1728900</v>
       </c>
-      <c r="R49" s="6">
+      <c r="S49" s="6">
         <v>1702400</v>
       </c>
-      <c r="S49" s="6">
+      <c r="T49" s="6">
         <v>1140200</v>
       </c>
-      <c r="T49" s="6">
+      <c r="U49" s="6">
         <v>1142800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1161600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1173600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1194300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1177300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>992700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1008600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1021400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1037600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>834200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>846700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>860600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>875200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>887700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>899700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>914700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>930500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>944800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>791100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>804800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>819000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>831600</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>847300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5350,7 +5464,7 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="6">
+      <c r="N50" s="3">
         <v>0</v>
       </c>
       <c r="O50" s="6">
@@ -5371,7 +5485,7 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="3">
+      <c r="U50" s="6">
         <v>0</v>
       </c>
       <c r="V50" s="3">
@@ -5437,8 +5551,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5472,7 +5589,7 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="6">
+      <c r="N51" s="3">
         <v>0</v>
       </c>
       <c r="O51" s="6">
@@ -5493,7 +5610,7 @@
       <c r="T51" s="6">
         <v>0</v>
       </c>
-      <c r="U51" s="3">
+      <c r="U51" s="6">
         <v>0</v>
       </c>
       <c r="V51" s="3">
@@ -5559,130 +5676,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>585600</v>
+      </c>
+      <c r="E52" s="3">
         <v>591400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>337900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>478600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>474300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>426400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>274500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>466900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>497100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>453300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>248300</v>
       </c>
-      <c r="N52" s="6">
+      <c r="O52" s="6">
         <v>504300</v>
       </c>
-      <c r="O52" s="6">
+      <c r="P52" s="6">
         <v>500200</v>
       </c>
-      <c r="P52" s="6">
+      <c r="Q52" s="6">
         <v>1380800</v>
       </c>
-      <c r="Q52" s="6">
+      <c r="R52" s="6">
         <v>1330000</v>
       </c>
-      <c r="R52" s="6">
+      <c r="S52" s="6">
         <v>1247000</v>
       </c>
-      <c r="S52" s="6">
+      <c r="T52" s="6">
         <v>1246700</v>
       </c>
-      <c r="T52" s="6">
+      <c r="U52" s="6">
         <v>1206700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1203000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1194000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1169200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1166900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1168400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1106900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1055600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1049700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>839200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>258300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>257400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>252000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>371200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>232500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>227200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>227000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>230300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>326800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>317000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>315100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>311700</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>299000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5716,7 +5839,7 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="6">
+      <c r="N53" s="3">
         <v>0</v>
       </c>
       <c r="O53" s="6">
@@ -5737,7 +5860,7 @@
       <c r="T53" s="6">
         <v>0</v>
       </c>
-      <c r="U53" s="3">
+      <c r="U53" s="6">
         <v>0</v>
       </c>
       <c r="V53" s="3">
@@ -5803,130 +5926,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12080300</v>
+      </c>
+      <c r="E54" s="3">
         <v>12098400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10153100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>9599300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9508700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9013500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8974500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9167000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>7225700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5722100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5669500</v>
       </c>
-      <c r="N54" s="6">
+      <c r="O54" s="6">
         <v>5431400</v>
       </c>
-      <c r="O54" s="6">
+      <c r="P54" s="6">
         <v>5155100</v>
       </c>
-      <c r="P54" s="6">
+      <c r="Q54" s="6">
         <v>5171600</v>
       </c>
-      <c r="Q54" s="6">
+      <c r="R54" s="6">
         <v>5137100</v>
       </c>
-      <c r="R54" s="6">
+      <c r="S54" s="6">
         <v>4968100</v>
       </c>
-      <c r="S54" s="6">
+      <c r="T54" s="6">
         <v>4361300</v>
       </c>
-      <c r="T54" s="6">
+      <c r="U54" s="6">
         <v>4395100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4386300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4213900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4122500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3999000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3950800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4140200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3999500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3768000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3357200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2662200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2612300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2546300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2468700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2273200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2527900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>2486700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>2418700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>2305200</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>2267700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>2191200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2096900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>2194100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5940,14 +6069,14 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-      <c r="N55" s="6"/>
+      <c r="N55" s="3"/>
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="6"/>
       <c r="R55" s="6"/>
       <c r="S55" s="6"/>
       <c r="T55" s="6"/>
-      <c r="U55" s="3"/>
+      <c r="U55" s="6"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
@@ -5969,8 +6098,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5984,14 +6114,14 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-      <c r="N56" s="6"/>
+      <c r="N56" s="3"/>
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
       <c r="S56" s="6"/>
       <c r="T56" s="6"/>
-      <c r="U56" s="3"/>
+      <c r="U56" s="6"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
@@ -6013,142 +6143,146 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>823700</v>
+      </c>
+      <c r="E57" s="3">
         <v>88200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>93500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>87300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>291800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>570200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>612300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>505400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>456300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>91200</v>
       </c>
-      <c r="N57" s="6">
+      <c r="O57" s="6">
         <v>598300</v>
       </c>
-      <c r="O57" s="6">
+      <c r="P57" s="6">
         <v>510000</v>
       </c>
-      <c r="P57" s="6">
+      <c r="Q57" s="6">
         <v>430100</v>
       </c>
-      <c r="Q57" s="6">
+      <c r="R57" s="6">
         <v>557200</v>
       </c>
-      <c r="R57" s="6">
+      <c r="S57" s="6">
         <v>454700</v>
       </c>
-      <c r="S57" s="6">
+      <c r="T57" s="6">
         <v>437200</v>
       </c>
-      <c r="T57" s="6">
+      <c r="U57" s="6">
         <v>360500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>417300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>363800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>340600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>271200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>350000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>290900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>306900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>236800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>291400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>247200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>219100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>211900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>256500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>212200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>243200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>210800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>221100</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>199700</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>222200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>194000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>239500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>192900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>425000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>49900</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
@@ -6156,42 +6290,42 @@
         <v>0</v>
       </c>
       <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>41600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>350000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>349700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>349500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>390900</v>
       </c>
-      <c r="N58" s="6">
-        <v>0</v>
-      </c>
       <c r="O58" s="6">
         <v>0</v>
       </c>
       <c r="P58" s="6">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6">
         <v>30000</v>
       </c>
-      <c r="Q58" s="6">
+      <c r="R58" s="6">
         <v>100000</v>
       </c>
-      <c r="R58" s="6">
+      <c r="S58" s="6">
         <v>150000</v>
-      </c>
-      <c r="S58" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="T58" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="U58" s="3" t="s">
+      <c r="U58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="V58" s="3" t="s">
@@ -6203,11 +6337,11 @@
       <c r="X58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="Z58" s="3">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="AA58" s="3">
         <v>350000</v>
@@ -6216,7 +6350,7 @@
         <v>350000</v>
       </c>
       <c r="AC58" s="3">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="AD58" s="3">
         <v>0</v>
@@ -6225,31 +6359,31 @@
         <v>0</v>
       </c>
       <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
         <v>50000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>100000</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
       <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>299900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>344800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>85000</v>
       </c>
-      <c r="AL58" s="3">
-        <v>0</v>
-      </c>
       <c r="AM58" s="3">
         <v>0</v>
       </c>
       <c r="AN58" s="3">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="AO58" s="3">
         <v>50000</v>
@@ -6257,496 +6391,511 @@
       <c r="AP58" s="3">
         <v>50000</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>50000</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1025100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1108500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>778400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>775300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>870500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>730600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>737400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>712800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>678600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>659900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>665000</v>
       </c>
-      <c r="N59" s="6">
+      <c r="O59" s="6">
         <v>665900</v>
       </c>
-      <c r="O59" s="6">
+      <c r="P59" s="6">
         <v>686300</v>
       </c>
-      <c r="P59" s="6">
+      <c r="Q59" s="6">
         <v>721200</v>
       </c>
-      <c r="Q59" s="6">
+      <c r="R59" s="6">
         <v>690500</v>
       </c>
-      <c r="R59" s="6">
+      <c r="S59" s="6">
         <v>652300</v>
       </c>
-      <c r="S59" s="6">
+      <c r="T59" s="6">
         <v>605300</v>
       </c>
-      <c r="T59" s="6">
+      <c r="U59" s="6">
         <v>600300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>553900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>543400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>586100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>521100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>446900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>477000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>494900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>425600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>381000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>371800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>391000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>369500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>352500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>329200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>327100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>310600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>336300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>320500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>322500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>331800</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>296100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>288400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1848800</v>
+      </c>
+      <c r="E60" s="3">
         <v>2162500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1635300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1406600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1496600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1300800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1370100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1675000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1533700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1465700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1590900</v>
       </c>
-      <c r="N60" s="6">
+      <c r="O60" s="6">
         <v>1264200</v>
       </c>
-      <c r="O60" s="6">
+      <c r="P60" s="6">
         <v>1196300</v>
       </c>
-      <c r="P60" s="6">
+      <c r="Q60" s="6">
         <v>1181400</v>
       </c>
-      <c r="Q60" s="6">
+      <c r="R60" s="6">
         <v>1347700</v>
       </c>
-      <c r="R60" s="6">
+      <c r="S60" s="6">
         <v>1257000</v>
       </c>
-      <c r="S60" s="6">
+      <c r="T60" s="6">
         <v>1042500</v>
       </c>
-      <c r="T60" s="6">
+      <c r="U60" s="6">
         <v>960800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>971200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>907200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>926700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>792300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>796800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1117900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1151900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1012400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>672400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>619000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>610200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>631400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>709000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>541300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>870100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>866200</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>642400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>520100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>544700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>575800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>585600</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>531300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2651400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2658400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2616400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2479100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2478100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2477200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2585100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2475200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>998900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>299800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>415100</v>
       </c>
-      <c r="N61" s="6">
+      <c r="O61" s="6">
         <v>648800</v>
       </c>
-      <c r="O61" s="6">
+      <c r="P61" s="6">
         <v>648600</v>
       </c>
-      <c r="P61" s="6">
+      <c r="Q61" s="6">
         <v>648300</v>
       </c>
-      <c r="Q61" s="6">
+      <c r="R61" s="6">
         <v>648100</v>
       </c>
-      <c r="R61" s="6">
+      <c r="S61" s="6">
         <v>647800</v>
       </c>
-      <c r="S61" s="6">
+      <c r="T61" s="6">
         <v>348000</v>
       </c>
-      <c r="T61" s="6">
+      <c r="U61" s="6">
         <v>347800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>347600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>347400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>347200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>347000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>346800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>346600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>346400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>346200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>346000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>345800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>345700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>345500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>345300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>345100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>344900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>344800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>644400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>644100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>643900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>643700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>643500</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>643300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>227800</v>
+      </c>
+      <c r="E62" s="3">
         <v>218000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>271200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>384500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>373000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>348600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>230600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>351000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>343400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>302000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>160300</v>
       </c>
-      <c r="N62" s="6">
+      <c r="O62" s="6">
         <v>303900</v>
       </c>
-      <c r="O62" s="6">
+      <c r="P62" s="6">
         <v>305200</v>
       </c>
-      <c r="P62" s="6">
+      <c r="Q62" s="6">
         <v>401100</v>
       </c>
-      <c r="Q62" s="6">
+      <c r="R62" s="6">
         <v>396200</v>
       </c>
-      <c r="R62" s="6">
+      <c r="S62" s="6">
         <v>355200</v>
       </c>
-      <c r="S62" s="6">
+      <c r="T62" s="6">
         <v>345600</v>
       </c>
-      <c r="T62" s="6">
+      <c r="U62" s="6">
         <v>326300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>326800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>328000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>331900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>317200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>314200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>280000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>244600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>251300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>235900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>217100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>225900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>203600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>126000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>129400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>124800</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>133400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>142700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>130200</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>127300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>131100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>126100</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>92700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6780,7 +6929,7 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="6">
+      <c r="N63" s="3">
         <v>0</v>
       </c>
       <c r="O63" s="6">
@@ -6801,7 +6950,7 @@
       <c r="T63" s="6">
         <v>0</v>
       </c>
-      <c r="U63" s="3">
+      <c r="U63" s="6">
         <v>0</v>
       </c>
       <c r="V63" s="3">
@@ -6867,8 +7016,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6902,7 +7054,7 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="6">
+      <c r="N64" s="3">
         <v>0</v>
       </c>
       <c r="O64" s="6">
@@ -6923,7 +7075,7 @@
       <c r="T64" s="6">
         <v>0</v>
       </c>
-      <c r="U64" s="3">
+      <c r="U64" s="6">
         <v>0</v>
       </c>
       <c r="V64" s="3">
@@ -6989,8 +7141,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7024,7 +7179,7 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="6">
+      <c r="N65" s="3">
         <v>0</v>
       </c>
       <c r="O65" s="6">
@@ -7045,7 +7200,7 @@
       <c r="T65" s="6">
         <v>0</v>
       </c>
-      <c r="U65" s="3">
+      <c r="U65" s="6">
         <v>0</v>
       </c>
       <c r="V65" s="3">
@@ -7111,130 +7266,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5222400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5536900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4679000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4400300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4502200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4237200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4300900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4603700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2964800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2154500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2265200</v>
       </c>
-      <c r="N66" s="6">
+      <c r="O66" s="6">
         <v>2317500</v>
       </c>
-      <c r="O66" s="6">
+      <c r="P66" s="6">
         <v>2246700</v>
       </c>
-      <c r="P66" s="6">
+      <c r="Q66" s="6">
         <v>2230700</v>
       </c>
-      <c r="Q66" s="6">
+      <c r="R66" s="6">
         <v>2392000</v>
       </c>
-      <c r="R66" s="6">
+      <c r="S66" s="6">
         <v>2260000</v>
       </c>
-      <c r="S66" s="6">
+      <c r="T66" s="6">
         <v>1736000</v>
       </c>
-      <c r="T66" s="6">
+      <c r="U66" s="6">
         <v>1634900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1645600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1582600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1605800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1456500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1457800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1744400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1742900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1610000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1254300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1181900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1181800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1180500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1180300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1015800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1339900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1344400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1429500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1294500</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1315900</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1350600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1355100</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1267300</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7248,14 +7409,14 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-      <c r="N67" s="6"/>
+      <c r="N67" s="3"/>
       <c r="O67" s="6"/>
       <c r="P67" s="6"/>
       <c r="Q67" s="6"/>
       <c r="R67" s="6"/>
       <c r="S67" s="6"/>
       <c r="T67" s="6"/>
-      <c r="U67" s="3"/>
+      <c r="U67" s="6"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
@@ -7277,8 +7438,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7312,7 +7474,7 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="6">
+      <c r="N68" s="3">
         <v>0</v>
       </c>
       <c r="O68" s="6">
@@ -7333,7 +7495,7 @@
       <c r="T68" s="6">
         <v>0</v>
       </c>
-      <c r="U68" s="3">
+      <c r="U68" s="6">
         <v>0</v>
       </c>
       <c r="V68" s="3">
@@ -7399,8 +7561,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7434,7 +7599,7 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="6">
+      <c r="N69" s="3">
         <v>0</v>
       </c>
       <c r="O69" s="6">
@@ -7455,7 +7620,7 @@
       <c r="T69" s="6">
         <v>0</v>
       </c>
-      <c r="U69" s="3">
+      <c r="U69" s="6">
         <v>0</v>
       </c>
       <c r="V69" s="3">
@@ -7521,8 +7686,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7556,7 +7724,7 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="6">
+      <c r="N70" s="3">
         <v>0</v>
       </c>
       <c r="O70" s="6">
@@ -7577,7 +7745,7 @@
       <c r="T70" s="6">
         <v>0</v>
       </c>
-      <c r="U70" s="3">
+      <c r="U70" s="6">
         <v>0</v>
       </c>
       <c r="V70" s="3">
@@ -7643,8 +7811,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7678,7 +7849,7 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="6">
+      <c r="N71" s="3">
         <v>0</v>
       </c>
       <c r="O71" s="6">
@@ -7699,7 +7870,7 @@
       <c r="T71" s="6">
         <v>0</v>
       </c>
-      <c r="U71" s="3">
+      <c r="U71" s="6">
         <v>0</v>
       </c>
       <c r="V71" s="3">
@@ -7765,130 +7936,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7803500</v>
+      </c>
+      <c r="E72" s="3">
         <v>7436400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7100800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6712600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6425500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6265400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5991900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5651700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5413500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5184000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4936400</v>
       </c>
-      <c r="N72" s="6">
+      <c r="O72" s="6">
         <v>4612500</v>
       </c>
-      <c r="O72" s="6">
+      <c r="P72" s="6">
         <v>4358200</v>
       </c>
-      <c r="P72" s="6">
+      <c r="Q72" s="6">
         <v>4137000</v>
       </c>
-      <c r="Q72" s="6">
+      <c r="R72" s="6">
         <v>3895200</v>
       </c>
-      <c r="R72" s="6">
+      <c r="S72" s="6">
         <v>3654800</v>
       </c>
-      <c r="S72" s="6">
+      <c r="T72" s="6">
         <v>3468500</v>
       </c>
-      <c r="T72" s="6">
+      <c r="U72" s="6">
         <v>3281600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3046300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2869700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2693400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2537500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2350300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2176600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2015000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1883700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1761700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1102000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1000500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>893300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>772700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>674300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>575000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>499800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>341000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>355400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>274300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>205200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>136900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>98400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7922,7 +8099,7 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="6">
+      <c r="N73" s="3">
         <v>0</v>
       </c>
       <c r="O73" s="6">
@@ -7943,7 +8120,7 @@
       <c r="T73" s="6">
         <v>0</v>
       </c>
-      <c r="U73" s="3">
+      <c r="U73" s="6">
         <v>0</v>
       </c>
       <c r="V73" s="3">
@@ -8009,8 +8186,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8044,7 +8224,7 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="6">
+      <c r="N74" s="3">
         <v>0</v>
       </c>
       <c r="O74" s="6">
@@ -8065,7 +8245,7 @@
       <c r="T74" s="6">
         <v>0</v>
       </c>
-      <c r="U74" s="3">
+      <c r="U74" s="6">
         <v>0</v>
       </c>
       <c r="V74" s="3">
@@ -8131,8 +8311,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8166,7 +8349,7 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="6">
+      <c r="N75" s="3">
         <v>0</v>
       </c>
       <c r="O75" s="6">
@@ -8187,7 +8370,7 @@
       <c r="T75" s="6">
         <v>0</v>
       </c>
-      <c r="U75" s="3">
+      <c r="U75" s="6">
         <v>0</v>
       </c>
       <c r="V75" s="3">
@@ -8253,130 +8436,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6858000</v>
+      </c>
+      <c r="E76" s="3">
         <v>6561500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5474200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5199000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5006500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4776300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4673600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4563300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4260900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3567600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3404300</v>
       </c>
-      <c r="N76" s="6">
+      <c r="O76" s="6">
         <v>3113900</v>
       </c>
-      <c r="O76" s="6">
+      <c r="P76" s="6">
         <v>2908500</v>
       </c>
-      <c r="P76" s="6">
+      <c r="Q76" s="6">
         <v>2940900</v>
       </c>
-      <c r="Q76" s="6">
+      <c r="R76" s="6">
         <v>2745100</v>
       </c>
-      <c r="R76" s="6">
+      <c r="S76" s="6">
         <v>2708100</v>
       </c>
-      <c r="S76" s="6">
+      <c r="T76" s="6">
         <v>2625200</v>
       </c>
-      <c r="T76" s="6">
+      <c r="U76" s="6">
         <v>2760200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2740700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2631300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2516700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2542400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2493000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2395700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2256600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2158000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2102900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1480300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1430500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1365800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1288400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1257400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1188000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1142300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>989200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1010700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>951800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>840600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>741800</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>926800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8410,7 +8599,7 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="6">
+      <c r="N77" s="3">
         <v>0</v>
       </c>
       <c r="O77" s="6">
@@ -8431,7 +8620,7 @@
       <c r="T77" s="6">
         <v>0</v>
       </c>
-      <c r="U77" s="3">
+      <c r="U77" s="6">
         <v>0</v>
       </c>
       <c r="V77" s="3">
@@ -8497,257 +8686,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.25">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="5">
+      <c r="O80" s="5">
         <v>45199</v>
       </c>
-      <c r="O80" s="5">
+      <c r="P80" s="5">
         <v>45107</v>
       </c>
-      <c r="P80" s="5">
+      <c r="Q80" s="5">
         <v>45016</v>
       </c>
-      <c r="Q80" s="5">
+      <c r="R80" s="5">
         <v>44926</v>
       </c>
-      <c r="R80" s="5">
+      <c r="S80" s="5">
         <v>44835</v>
       </c>
-      <c r="S80" s="5">
+      <c r="T80" s="5">
         <v>44744</v>
       </c>
-      <c r="T80" s="5">
+      <c r="U80" s="5">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44563</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44198</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44100</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44009</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43918</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43827</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43463</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43099</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>367100</v>
+      </c>
+      <c r="E81" s="3">
         <v>335700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>388100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>287100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>160100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>273600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>340200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>238100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>229500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>247600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>323900</v>
       </c>
-      <c r="N81" s="6">
+      <c r="O81" s="6">
         <v>254300</v>
       </c>
-      <c r="O81" s="6">
+      <c r="P81" s="6">
         <v>221100</v>
       </c>
-      <c r="P81" s="6">
+      <c r="Q81" s="6">
         <v>241800</v>
       </c>
-      <c r="Q81" s="6">
+      <c r="R81" s="6">
         <v>240400</v>
       </c>
-      <c r="R81" s="6">
+      <c r="S81" s="6">
         <v>186300</v>
       </c>
-      <c r="S81" s="6">
+      <c r="T81" s="6">
         <v>186900</v>
       </c>
-      <c r="T81" s="6">
+      <c r="U81" s="6">
         <v>235300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>176600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>176300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>155900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>187200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>173700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>161600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>131300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>124000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>659700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>101500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>107200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>120600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>98400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>99300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>75100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>72900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-14400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>81200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>69100</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>68300</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>38500</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>64700</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8761,14 +8959,14 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-      <c r="N82" s="6"/>
+      <c r="N82" s="3"/>
       <c r="O82" s="6"/>
       <c r="P82" s="6"/>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
       <c r="S82" s="6"/>
       <c r="T82" s="6"/>
-      <c r="U82" s="3"/>
+      <c r="U82" s="6"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
@@ -8790,97 +8988,98 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>32600</v>
+      </c>
+      <c r="E83" s="3">
         <v>27500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>28300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>27500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>22800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>22000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>19900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>21900</v>
       </c>
-      <c r="N83" s="6">
+      <c r="O83" s="6">
         <v>15900</v>
       </c>
-      <c r="O83" s="6">
+      <c r="P83" s="6">
         <v>19000</v>
       </c>
-      <c r="P83" s="6">
+      <c r="Q83" s="6">
         <v>34400</v>
       </c>
-      <c r="Q83" s="6">
+      <c r="R83" s="6">
         <v>33900</v>
       </c>
-      <c r="R83" s="6">
+      <c r="S83" s="6">
         <v>30500</v>
       </c>
-      <c r="S83" s="6">
+      <c r="T83" s="6">
         <v>32900</v>
       </c>
-      <c r="T83" s="6">
+      <c r="U83" s="6">
         <v>34800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>35300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>35200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>35600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>36200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>38600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>37100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>36600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>33300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>30200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31500</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>29700</v>
       </c>
       <c r="AG83" s="3">
         <v>29700</v>
@@ -8889,31 +9088,34 @@
         <v>29700</v>
       </c>
       <c r="AI83" s="3">
+        <v>29700</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>29400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>28900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>28300</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>29400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>28900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>29900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>27000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8947,7 +9149,7 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="6">
+      <c r="N84" s="3">
         <v>0</v>
       </c>
       <c r="O84" s="6">
@@ -8968,7 +9170,7 @@
       <c r="T84" s="6">
         <v>0</v>
       </c>
-      <c r="U84" s="3">
+      <c r="U84" s="6">
         <v>0</v>
       </c>
       <c r="V84" s="3">
@@ -9034,8 +9236,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9069,7 +9274,7 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="6">
+      <c r="N85" s="3">
         <v>0</v>
       </c>
       <c r="O85" s="6">
@@ -9090,7 +9295,7 @@
       <c r="T85" s="6">
         <v>0</v>
       </c>
-      <c r="U85" s="3">
+      <c r="U85" s="6">
         <v>0</v>
       </c>
       <c r="V85" s="3">
@@ -9156,8 +9361,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9191,7 +9399,7 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="6">
+      <c r="N86" s="3">
         <v>0</v>
       </c>
       <c r="O86" s="6">
@@ -9212,7 +9420,7 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="3">
+      <c r="U86" s="6">
         <v>0</v>
       </c>
       <c r="V86" s="3">
@@ -9278,8 +9486,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9313,7 +9524,7 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="6">
+      <c r="N87" s="3">
         <v>0</v>
       </c>
       <c r="O87" s="6">
@@ -9334,7 +9545,7 @@
       <c r="T87" s="6">
         <v>0</v>
       </c>
-      <c r="U87" s="3">
+      <c r="U87" s="6">
         <v>0</v>
       </c>
       <c r="V87" s="3">
@@ -9400,8 +9611,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9435,7 +9649,7 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="6">
+      <c r="N88" s="3">
         <v>0</v>
       </c>
       <c r="O88" s="6">
@@ -9456,7 +9670,7 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="3">
+      <c r="U88" s="6">
         <v>0</v>
       </c>
       <c r="V88" s="3">
@@ -9522,130 +9736,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>634900</v>
+      </c>
+      <c r="E89" s="3">
         <v>355800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>553500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>310700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>377600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>487000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>441400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>410000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>156000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>253200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>272100</v>
       </c>
-      <c r="N89" s="6">
+      <c r="O89" s="6">
         <v>395900</v>
       </c>
-      <c r="O89" s="6">
+      <c r="P89" s="6">
         <v>413800</v>
       </c>
-      <c r="P89" s="6">
+      <c r="Q89" s="6">
         <v>267400</v>
       </c>
-      <c r="Q89" s="6">
+      <c r="R89" s="6">
         <v>263600</v>
       </c>
-      <c r="R89" s="6">
+      <c r="S89" s="6">
         <v>317100</v>
       </c>
-      <c r="S89" s="6">
+      <c r="T89" s="6">
         <v>324500</v>
       </c>
-      <c r="T89" s="6">
+      <c r="U89" s="6">
         <v>336600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>215900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>296300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>380400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>208400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>135500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>206600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>345100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>217700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>159300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>138500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>246400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>185400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>131900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>110000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>205300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>157600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>126900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>89300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>162100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>92400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>196900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9659,14 +9879,14 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-      <c r="N90" s="6"/>
+      <c r="N90" s="3"/>
       <c r="O90" s="6"/>
       <c r="P90" s="6"/>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
       <c r="S90" s="6"/>
       <c r="T90" s="6"/>
-      <c r="U90" s="3"/>
+      <c r="U90" s="6"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
@@ -9688,130 +9908,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-41000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-33700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-44100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-23100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-37200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-26500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-33700</v>
       </c>
-      <c r="N91" s="6">
+      <c r="O91" s="6">
         <v>-22000</v>
       </c>
-      <c r="O91" s="6">
+      <c r="P91" s="6">
         <v>-19900</v>
       </c>
-      <c r="P91" s="6">
+      <c r="Q91" s="6">
         <v>-26700</v>
       </c>
-      <c r="Q91" s="6">
+      <c r="R91" s="6">
         <v>-36900</v>
       </c>
-      <c r="R91" s="6">
+      <c r="S91" s="6">
         <v>-44300</v>
       </c>
-      <c r="S91" s="6">
+      <c r="T91" s="6">
         <v>-24100</v>
       </c>
-      <c r="T91" s="6">
+      <c r="U91" s="6">
         <v>-18900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-15300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-14200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-20200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-21400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17000</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-15300</v>
       </c>
       <c r="AF91" s="3">
         <v>-15300</v>
       </c>
       <c r="AG91" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-19700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-13100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-18200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-12600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-14800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-11300</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-14200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9845,7 +10069,7 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="6">
+      <c r="N92" s="3">
         <v>0</v>
       </c>
       <c r="O92" s="6">
@@ -9866,7 +10090,7 @@
       <c r="T92" s="6">
         <v>0</v>
       </c>
-      <c r="U92" s="3">
+      <c r="U92" s="6">
         <v>0</v>
       </c>
       <c r="V92" s="3">
@@ -9932,8 +10156,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9967,7 +10194,7 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="6">
+      <c r="N93" s="3">
         <v>0</v>
       </c>
       <c r="O93" s="6">
@@ -9988,7 +10215,7 @@
       <c r="T93" s="6">
         <v>0</v>
       </c>
-      <c r="U93" s="3">
+      <c r="U93" s="6">
         <v>0</v>
       </c>
       <c r="V93" s="3">
@@ -10054,130 +10281,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2112000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-88800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-174300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-175600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-40000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-39300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-678100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-79800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-98700</v>
       </c>
-      <c r="N94" s="6">
+      <c r="O94" s="6">
         <v>-183800</v>
       </c>
-      <c r="O94" s="6">
+      <c r="P94" s="6">
         <v>-94100</v>
       </c>
-      <c r="P94" s="6">
+      <c r="Q94" s="6">
         <v>-35700</v>
       </c>
-      <c r="Q94" s="6">
+      <c r="R94" s="6">
         <v>-64200</v>
       </c>
-      <c r="R94" s="6">
+      <c r="S94" s="6">
         <v>-605500</v>
       </c>
-      <c r="S94" s="6">
+      <c r="T94" s="6">
         <v>-49100</v>
       </c>
-      <c r="T94" s="6">
+      <c r="U94" s="6">
         <v>-19900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-23100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-18100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-45600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-206200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-30900</v>
-      </c>
-      <c r="Z94" s="3">
-        <v>-22700</v>
       </c>
       <c r="AA94" s="3">
         <v>-22700</v>
       </c>
       <c r="AB94" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="AC94" s="3">
         <v>-216000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-27100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-17000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-15700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-46000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-132100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-10700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-18000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-13100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-160500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-14700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10191,14 +10424,14 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-      <c r="N95" s="6"/>
+      <c r="N95" s="3"/>
       <c r="O95" s="6"/>
       <c r="P95" s="6"/>
       <c r="Q95" s="6"/>
       <c r="R95" s="6"/>
       <c r="S95" s="6"/>
       <c r="T95" s="6"/>
-      <c r="U95" s="3"/>
+      <c r="U95" s="6"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
@@ -10220,8 +10453,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10255,14 +10489,14 @@
       <c r="M96" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="N96" s="6" t="s">
+      <c r="N96" s="3" t="s">
         <v>24</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="P96" s="6">
-        <v>0</v>
+      <c r="P96" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="Q96" s="6">
         <v>0</v>
@@ -10276,7 +10510,7 @@
       <c r="T96" s="6">
         <v>0</v>
       </c>
-      <c r="U96" s="3">
+      <c r="U96" s="6">
         <v>0</v>
       </c>
       <c r="V96" s="3">
@@ -10342,8 +10576,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10377,7 +10614,7 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="6">
+      <c r="N97" s="3">
         <v>0</v>
       </c>
       <c r="O97" s="6">
@@ -10398,7 +10635,7 @@
       <c r="T97" s="6">
         <v>0</v>
       </c>
-      <c r="U97" s="3">
+      <c r="U97" s="6">
         <v>0</v>
       </c>
       <c r="V97" s="3">
@@ -10464,8 +10701,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10499,7 +10739,7 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="6">
+      <c r="N98" s="3">
         <v>0</v>
       </c>
       <c r="O98" s="6">
@@ -10520,7 +10760,7 @@
       <c r="T98" s="6">
         <v>0</v>
       </c>
-      <c r="U98" s="3">
+      <c r="U98" s="6">
         <v>0</v>
       </c>
       <c r="V98" s="3">
@@ -10586,8 +10826,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10621,7 +10864,7 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="6">
+      <c r="N99" s="3">
         <v>0</v>
       </c>
       <c r="O99" s="6">
@@ -10642,7 +10885,7 @@
       <c r="T99" s="6">
         <v>0</v>
       </c>
-      <c r="U99" s="3">
+      <c r="U99" s="6">
         <v>0</v>
       </c>
       <c r="V99" s="3">
@@ -10708,370 +10951,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-626400</v>
+      </c>
+      <c r="E100" s="3">
         <v>174500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-213900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-194100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-195200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-345800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-511100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1335000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>574800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-159400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-137600</v>
       </c>
-      <c r="N100" s="6">
+      <c r="O100" s="6">
         <v>-114400</v>
       </c>
-      <c r="O100" s="6">
+      <c r="P100" s="6">
         <v>-354300</v>
       </c>
-      <c r="P100" s="6">
+      <c r="Q100" s="6">
         <v>-197400</v>
       </c>
-      <c r="Q100" s="6">
+      <c r="R100" s="6">
         <v>-357200</v>
       </c>
-      <c r="R100" s="6">
+      <c r="S100" s="6">
         <v>313500</v>
       </c>
-      <c r="S100" s="6">
+      <c r="T100" s="6">
         <v>-352700</v>
       </c>
-      <c r="T100" s="6">
+      <c r="U100" s="6">
         <v>-260700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-115700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-108800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-237100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-182300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-501200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-79100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-80800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>245800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-86900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-88100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-134900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-134100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-7600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-367000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-96300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-97100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>39400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-62900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-46100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-500</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-236600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-244100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E101" s="3">
         <v>14200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-32200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>21400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-6200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>10400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-9700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>14000</v>
       </c>
-      <c r="N101" s="6">
+      <c r="O101" s="6">
         <v>-28600</v>
       </c>
-      <c r="O101" s="6">
+      <c r="P101" s="6">
         <v>-28000</v>
       </c>
-      <c r="P101" s="6">
+      <c r="Q101" s="6">
         <v>300</v>
       </c>
-      <c r="Q101" s="6">
+      <c r="R101" s="6">
         <v>14000</v>
       </c>
-      <c r="R101" s="6">
+      <c r="S101" s="6">
         <v>-28600</v>
       </c>
-      <c r="S101" s="6">
+      <c r="T101" s="6">
         <v>-28000</v>
       </c>
-      <c r="T101" s="6">
+      <c r="U101" s="6">
         <v>-10200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>6500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>18400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>12600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>4600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-7300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-18400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>11400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>4100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-800</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>8400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>1800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-14100</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.25">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.25">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>33800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1594600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>248100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-69500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>45100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>133600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-142000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1727100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>46500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>4300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>46200</v>
       </c>
-      <c r="N102" s="6">
+      <c r="O102" s="6">
         <v>88100</v>
       </c>
-      <c r="O102" s="6">
+      <c r="P102" s="6">
         <v>-43000</v>
       </c>
-      <c r="P102" s="6">
+      <c r="Q102" s="6">
         <v>34600</v>
       </c>
-      <c r="Q102" s="6">
+      <c r="R102" s="6">
         <v>-143700</v>
       </c>
-      <c r="R102" s="6">
+      <c r="S102" s="6">
         <v>-3500</v>
       </c>
-      <c r="S102" s="6">
+      <c r="T102" s="6">
         <v>-105200</v>
       </c>
-      <c r="T102" s="6">
+      <c r="U102" s="6">
         <v>45800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>75100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>166700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>104200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-185500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-378100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>117400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>242900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>241100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>50000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>21800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>94500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>5600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-11300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-275000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>72600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>58900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>22300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>111900</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>78900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-59100</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-145200</v>
       </c>
     </row>
